--- a/exports/489_buenos-aires.xlsx
+++ b/exports/489_buenos-aires.xlsx
@@ -16425,22 +16425,22 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>79670987</t>
+          <t>76961463</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>TORPOCO</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t>ALVAREZ</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>BON JOVI LEO DAN</t>
+          <t>EDVIS ANLLE</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -16449,16 +16449,16 @@
         </is>
       </c>
       <c r="F255" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>08/05/2016</t>
+          <t>09/06/2000</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -16473,7 +16473,7 @@
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t>01/09/2025</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">

--- a/exports/489_buenos-aires.xlsx
+++ b/exports/489_buenos-aires.xlsx
@@ -16425,22 +16425,22 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>76961463</t>
+          <t>79670987</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>TORPOCO</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>ALVAREZ</t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>EDVIS ANLLE</t>
+          <t>BON JOVI LEO DAN</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -16449,16 +16449,16 @@
         </is>
       </c>
       <c r="F255" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>09/06/2000</t>
+          <t>08/05/2016</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -16473,7 +16473,7 @@
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>01/09/2025</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">

--- a/exports/489_buenos-aires.xlsx
+++ b/exports/489_buenos-aires.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M310"/>
+  <dimension ref="A1:M308"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9747,35 +9747,35 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>73658338</t>
+          <t>74255582</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>MINCAMI</t>
+          <t>MONTAÑO</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>MARCOS</t>
+          <t>BERROCAL</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>YULIANA DIANA</t>
+          <t>RAUL ALEXIS</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>16/12/2001</t>
+          <t>26/11/2005</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9785,7 +9785,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -9795,7 +9795,7 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>27/10/2025</t>
+          <t>14/11/2013</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -9810,7 +9810,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>74255582</t>
+          <t>61567986</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9825,20 +9825,20 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>RAUL ALEXIS</t>
+          <t>YOISY ROSA</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>26/11/2005</t>
+          <t>28/10/2008</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -9858,7 +9858,7 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>14/11/2013</t>
+          <t>10/03/2014</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -9873,7 +9873,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>61567986</t>
+          <t>42252116</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9883,35 +9883,35 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>BERROCAL</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>YOISY ROSA</t>
+          <t>RAUL HENRY</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>28/10/2008</t>
+          <t>30/01/1984</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -9921,7 +9921,7 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>10/03/2014</t>
+          <t>22/10/2013</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -9936,7 +9936,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>42252116</t>
+          <t>45744893</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9951,7 +9951,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>RAUL HENRY</t>
+          <t>MANUEL</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -9960,11 +9960,11 @@
         </is>
       </c>
       <c r="F152" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>30/01/1984</t>
+          <t>10/10/1988</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -9984,7 +9984,7 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>22/10/2013</t>
+          <t>25/05/2018</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -9999,7 +9999,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>45744893</t>
+          <t>60303725</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -10014,7 +10014,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>MANUEL</t>
+          <t>OLICK ENRRIQUE</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -10023,21 +10023,21 @@
         </is>
       </c>
       <c r="F153" t="n">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>10/10/1988</t>
+          <t>22/11/2007</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -10047,7 +10047,7 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>25/05/2018</t>
+          <t>28/05/2018</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -10062,7 +10062,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>60303725</t>
+          <t>62291313</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -10077,7 +10077,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>OLICK ENRRIQUE</t>
+          <t>DIDIEE HENRY</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -10086,16 +10086,16 @@
         </is>
       </c>
       <c r="F154" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>22/11/2007</t>
+          <t>18/06/2009</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -10110,7 +10110,7 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>28/05/2018</t>
+          <t>29/05/2018</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -10125,7 +10125,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>62291313</t>
+          <t>92254018</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -10140,25 +10140,25 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>DIDIEE HENRY</t>
+          <t>MADY ANDREA</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>18/06/2009</t>
+          <t>02/03/2021</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -10173,7 +10173,7 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>29/05/2018</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -10188,22 +10188,22 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>92254018</t>
+          <t>75536152</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>MONTAÑO</t>
+          <t>MORATILLO</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>MADY ANDREA</t>
+          <t>ADA ELIZABETH</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -10212,21 +10212,21 @@
         </is>
       </c>
       <c r="F156" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>02/03/2021</t>
+          <t>15/10/1999</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -10236,7 +10236,7 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>02/09/2014</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -10251,22 +10251,22 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>75536152</t>
+          <t>20093135</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>MORATILLO</t>
+          <t>OCAÑO</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>SUAREZ</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>ADA ELIZABETH</t>
+          <t>RICARDA</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -10275,16 +10275,16 @@
         </is>
       </c>
       <c r="F157" t="n">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>15/10/1999</t>
+          <t>08/02/1974</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -10299,7 +10299,7 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>02/09/2014</t>
+          <t>16/09/2014</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -10314,22 +10314,22 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>20093135</t>
+          <t>40414355</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>OCAÑO</t>
+          <t>ORE</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>SUAREZ</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>RICARDA</t>
+          <t>MIRIAM YULIANA</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -10338,11 +10338,11 @@
         </is>
       </c>
       <c r="F158" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>08/02/1974</t>
+          <t>26/10/1979</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10362,7 +10362,7 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>16/09/2014</t>
+          <t>15/05/2019</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -10377,35 +10377,35 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>40414355</t>
+          <t>46687881</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>ORE</t>
+          <t>ORIHUELA</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>ESPINAL</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>MIRIAM YULIANA</t>
+          <t>WILMER</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F159" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>26/10/1979</t>
+          <t>19/11/1990</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10425,7 +10425,7 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>15/05/2019</t>
+          <t>29/08/2018</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -10440,35 +10440,35 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>46687881</t>
+          <t>41736806</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>ORIHUELA</t>
+          <t>OSORIO</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>ESPINAL</t>
+          <t>ARMAULIA</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>WILMER</t>
+          <t>LIZ MARGA</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F160" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>19/11/1990</t>
+          <t>17/12/1982</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10488,7 +10488,7 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>29/08/2018</t>
+          <t>20/03/2013</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -10503,7 +10503,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>41736806</t>
+          <t>20968635</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10513,30 +10513,30 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>ARMAULIA</t>
+          <t>CURO</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LIZ MARGA</t>
+          <t>ANTONIO</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F161" t="n">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>17/12/1982</t>
+          <t>13/06/1944</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>20/03/2013</t>
+          <t>31/01/2020</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -10566,22 +10566,22 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>20968635</t>
+          <t>20998072</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>OSORIO</t>
+          <t>PAJAR</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>CURO</t>
+          <t>PASTRANA</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>ANTONIO</t>
+          <t>CRISTOBAL</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -10590,11 +10590,11 @@
         </is>
       </c>
       <c r="F162" t="n">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>13/06/1944</t>
+          <t>22/08/1957</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>31/01/2020</t>
+          <t>23/04/2015</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -10629,22 +10629,22 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>20998072</t>
+          <t>61712644</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>PAJAR</t>
+          <t>PARAGUAY</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>PASTRANA</t>
+          <t>OCAÑO</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>CRISTOBAL</t>
+          <t>YANDER</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -10653,21 +10653,21 @@
         </is>
       </c>
       <c r="F163" t="n">
-        <v>69</v>
+        <v>16</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>22/08/1957</t>
+          <t>28/11/2010</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -10677,7 +10677,7 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>23/04/2015</t>
+          <t>21/10/2014</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -10692,7 +10692,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>61712644</t>
+          <t>20995840</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10702,12 +10702,12 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>OCAÑO</t>
+          <t>PASTRANA</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>YANDER</t>
+          <t>ROLANDO</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -10716,21 +10716,21 @@
         </is>
       </c>
       <c r="F164" t="n">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>28/11/2010</t>
+          <t>20/09/1969</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -10740,7 +10740,7 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>21/10/2014</t>
+          <t>16/09/2014</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -10755,7 +10755,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>20995840</t>
+          <t>42330351</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10770,7 +10770,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>ROLANDO</t>
+          <t>RAUL</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -10779,11 +10779,11 @@
         </is>
       </c>
       <c r="F165" t="n">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>20/09/1969</t>
+          <t>21/07/1982</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -10803,7 +10803,7 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>16/09/2014</t>
+          <t>18/01/2013</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -10818,7 +10818,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>42330351</t>
+          <t>60203492</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -10828,35 +10828,35 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>PASTRANA</t>
+          <t>VELIZ</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>RAUL</t>
+          <t>ARELY MIREYA</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F166" t="n">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>21/07/1982</t>
+          <t>20/01/2007</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -10866,7 +10866,7 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>18/01/2013</t>
+          <t>14/11/2013</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -10881,7 +10881,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>60203492</t>
+          <t>61634651</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10896,7 +10896,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>ARELY MIREYA</t>
+          <t>YADIRA YARUMI</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -10905,11 +10905,11 @@
         </is>
       </c>
       <c r="F167" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>20/01/2007</t>
+          <t>26/11/2008</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -10944,7 +10944,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>61634651</t>
+          <t>62188600</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -10959,7 +10959,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>YADIRA YARUMI</t>
+          <t>SHIRLE DEYSI</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -10968,16 +10968,16 @@
         </is>
       </c>
       <c r="F168" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>26/11/2008</t>
+          <t>09/07/2010</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -10992,7 +10992,7 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>14/11/2013</t>
+          <t>10/03/2014</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -11007,7 +11007,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>62188600</t>
+          <t>63152290</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -11022,7 +11022,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>SHIRLE DEYSI</t>
+          <t>MAYUMI KIARA</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -11031,11 +11031,11 @@
         </is>
       </c>
       <c r="F169" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>09/07/2010</t>
+          <t>21/05/2012</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -11055,7 +11055,7 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>10/03/2014</t>
+          <t>14/11/2013</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -11070,40 +11070,40 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>63152290</t>
+          <t>60596969</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>PARAGUAY</t>
+          <t>PINEDO</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>VELIZ</t>
+          <t>HINOSTROZA</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>MAYUMI KIARA</t>
+          <t>CARLOS FRANCO</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F170" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>21/05/2012</t>
+          <t>24/07/2005</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -11118,7 +11118,7 @@
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>14/11/2013</t>
+          <t>24/06/2013</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -11133,45 +11133,45 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>60596969</t>
+          <t>20968095</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>PINEDO</t>
+          <t>PIZARRO</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>HINOSTROZA</t>
+          <t>BALTAZAR</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>CARLOS FRANCO</t>
+          <t>MARIA TEODORA</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F171" t="n">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>24/07/2005</t>
+          <t>02/08/1958</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -11181,7 +11181,7 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>24/06/2013</t>
+          <t>11/08/2014</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -11196,22 +11196,22 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>20968095</t>
+          <t>46203785</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>PIZARRO</t>
+          <t>PORRAS</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>BALTAZAR</t>
+          <t>HUAYCAÑI</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>MARIA TEODORA</t>
+          <t>AYDEE MARGARITA</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -11220,16 +11220,16 @@
         </is>
       </c>
       <c r="F172" t="n">
-        <v>68</v>
+        <v>37</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>02/08/1958</t>
+          <t>31/12/1989</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -11244,7 +11244,7 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>11/08/2014</t>
+          <t>16/09/2013</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -11259,40 +11259,40 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>46203785</t>
+          <t>20968061</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>PORRAS</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>HUAYCAÑI</t>
+          <t>CHAVEZ</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>AYDEE MARGARITA</t>
+          <t>MARIO</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>37</v>
+        <v>78</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>31/12/1989</t>
+          <t>12/10/1948</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -11307,7 +11307,7 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>16/09/2013</t>
+          <t>16/12/2015</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -11322,7 +11322,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>20968061</t>
+          <t>20983586</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11332,25 +11332,25 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>CHAVEZ</t>
+          <t>CONTRERAS DE URETA</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>MARIO</t>
+          <t>NELLY ROSA</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>12/10/1948</t>
+          <t>31/07/1954</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -11360,7 +11360,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -11370,7 +11370,7 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>16/12/2015</t>
+          <t>17/05/2012</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -11385,7 +11385,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>20983586</t>
+          <t>20965181</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11395,12 +11395,12 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>CONTRERAS DE URETA</t>
+          <t>DE CAMPOS</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>NELLY ROSA</t>
+          <t>FLOR ANGELICA</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -11409,11 +11409,11 @@
         </is>
       </c>
       <c r="F175" t="n">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>31/07/1954</t>
+          <t>02/10/1964</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -11423,7 +11423,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -11433,7 +11433,7 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>17/05/2012</t>
+          <t>11/02/2013</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -11448,7 +11448,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>20965181</t>
+          <t>20443727</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11458,35 +11458,35 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>DE CAMPOS</t>
+          <t>LEON</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>FLOR ANGELICA</t>
+          <t>JOSE LUIS</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F176" t="n">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>02/10/1964</t>
+          <t>25/01/1977</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -11496,7 +11496,7 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>11/02/2013</t>
+          <t>23/10/2013</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -11511,7 +11511,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>20443727</t>
+          <t>49048027</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11521,12 +11521,12 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>LEON</t>
+          <t>MATEO</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>JOSE LUIS</t>
+          <t>LUIS ALBERTO</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -11535,11 +11535,11 @@
         </is>
       </c>
       <c r="F177" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>25/01/1977</t>
+          <t>02/03/1986</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -11549,7 +11549,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -11559,7 +11559,7 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>23/10/2013</t>
+          <t>16/02/2022</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -11574,7 +11574,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>49048027</t>
+          <t>94197505</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11584,35 +11584,35 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>MATEO</t>
+          <t>PARAGUAY</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>LUIS ALBERTO</t>
+          <t>LUCIANA ESTEICY</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F178" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>02/03/1986</t>
+          <t>02/04/2025</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -11622,7 +11622,7 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>16/02/2022</t>
+          <t>24/04/2025</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -11637,7 +11637,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>94197505</t>
+          <t>20968071</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11647,35 +11647,35 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>PARAGUAY</t>
+          <t>PAREDES</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>LUCIANA ESTEICY</t>
+          <t>FLORENTINO</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F179" t="n">
-        <v>1</v>
+        <v>99</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>02/04/2025</t>
+          <t>16/10/1927</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -11685,7 +11685,7 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>24/04/2025</t>
+          <t>20/08/2014</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -11700,7 +11700,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>20968071</t>
+          <t>77488864</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11710,12 +11710,12 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>PAREDES</t>
+          <t>RAMOS</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>FLORENTINO</t>
+          <t>BRAYAN HERLYN</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -11724,21 +11724,21 @@
         </is>
       </c>
       <c r="F180" t="n">
-        <v>99</v>
+        <v>26</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>16/10/1927</t>
+          <t>08/01/2000</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -11748,7 +11748,7 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>20/08/2014</t>
+          <t>17/05/2022</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -11763,7 +11763,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>77488864</t>
+          <t>77488865</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>BRAYAN HERLYN</t>
+          <t>BREYNER FRANK</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -11787,11 +11787,11 @@
         </is>
       </c>
       <c r="F181" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>08/01/2000</t>
+          <t>18/08/2001</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -11811,7 +11811,7 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>17/05/2022</t>
+          <t>16/07/2021</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -11826,7 +11826,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>77488865</t>
+          <t>60303738</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11841,7 +11841,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>BREYNER FRANK</t>
+          <t>DEYVIS MARIO</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -11850,11 +11850,11 @@
         </is>
       </c>
       <c r="F182" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>18/08/2001</t>
+          <t>13/12/2007</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -11864,7 +11864,7 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -11874,7 +11874,7 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>16/07/2021</t>
+          <t>10/03/2014</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -11889,7 +11889,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>60303738</t>
+          <t>60369311</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -11899,12 +11899,12 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>RAMOS</t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>DEYVIS MARIO</t>
+          <t>DARLYN ANTONY</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -11913,11 +11913,11 @@
         </is>
       </c>
       <c r="F183" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>13/12/2007</t>
+          <t>09/03/2008</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -11937,7 +11937,7 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>10/03/2014</t>
+          <t>23/09/2011</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -11952,7 +11952,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>60369311</t>
+          <t>20998076</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11962,35 +11962,35 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t>YALLICO</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>DARLYN ANTONY</t>
+          <t>VILMA MARIA</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>09/03/2008</t>
+          <t>06/04/1975</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -12000,7 +12000,7 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>23/09/2011</t>
+          <t>16/12/2015</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
@@ -12015,7 +12015,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>20998076</t>
+          <t>41171139</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -12030,20 +12030,20 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>VILMA MARIA</t>
+          <t>ALFONSO LOLO</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>06/04/1975</t>
+          <t>13/10/1980</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -12063,7 +12063,7 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>16/12/2015</t>
+          <t>20/08/2014</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -12078,7 +12078,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>41171139</t>
+          <t>47242401</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -12093,20 +12093,20 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>ALFONSO LOLO</t>
+          <t>DIVEY TEOFILA</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F186" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>13/10/1980</t>
+          <t>19/04/1990</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -12126,7 +12126,7 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>20/08/2014</t>
+          <t>02/09/2015</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -12141,22 +12141,22 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>47242401</t>
+          <t>62188635</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>QUIÑONEZ</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>YALLICO</t>
+          <t>AVILA</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>DIVEY TEOFILA</t>
+          <t>MAYLI YULISA</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -12165,16 +12165,16 @@
         </is>
       </c>
       <c r="F187" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>19/04/1990</t>
+          <t>16/10/2006</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -12189,7 +12189,7 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>02/09/2015</t>
+          <t>17/09/2020</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -12204,7 +12204,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>62188635</t>
+          <t>78169955</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -12219,30 +12219,30 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>MAYLI YULISA</t>
+          <t>JOEL TONI</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F188" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>16/10/2006</t>
+          <t>25/06/2013</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -12252,7 +12252,7 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>17/09/2020</t>
+          <t>31/10/2018</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -12267,7 +12267,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>78169955</t>
+          <t>44500695</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -12277,12 +12277,12 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>AVILA</t>
+          <t>BENITO</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>JOEL TONI</t>
+          <t>JOSE</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -12291,21 +12291,21 @@
         </is>
       </c>
       <c r="F189" t="n">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>25/06/2013</t>
+          <t>28/08/1987</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -12315,7 +12315,7 @@
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>31/10/2018</t>
+          <t>21/03/2024</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
@@ -12330,45 +12330,45 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>44500695</t>
+          <t>93735599</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>QUIÑONEZ</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>BENITO</t>
+          <t>GRABIEL</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>JOSE</t>
+          <t>DEBORA ABIGAIL</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F190" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>28/08/1987</t>
+          <t>25/02/2024</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -12378,7 +12378,7 @@
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>21/03/2024</t>
+          <t>09/07/2024</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -12393,7 +12393,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>93735599</t>
+          <t>90050379</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12403,35 +12403,35 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>GRABIEL</t>
+          <t>PISKULICH</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>DEBORA ABIGAIL</t>
+          <t>GEDEON</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F191" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>25/02/2024</t>
+          <t>26/09/1999</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -12441,7 +12441,7 @@
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>09/07/2024</t>
+          <t>12/07/2024</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
@@ -12456,45 +12456,45 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>90050379</t>
+          <t>46096492</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>RAMOS</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>PISKULICH</t>
+          <t>ESPINOZA</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>GEDEON</t>
+          <t>GRIMALDA</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F192" t="n">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>26/09/1999</t>
+          <t>16/04/1981</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
@@ -12504,7 +12504,7 @@
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>12/07/2024</t>
+          <t>20/08/2014</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
@@ -12519,7 +12519,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>46096492</t>
+          <t>76899118</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12529,35 +12529,35 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>ESPINOZA</t>
+          <t>RAMOS</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>GRIMALDA</t>
+          <t>SERGIO FREDDY</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F193" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>16/04/1981</t>
+          <t>11/05/2011</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
@@ -12567,7 +12567,7 @@
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>20/08/2014</t>
+          <t>16/02/2022</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
@@ -12582,7 +12582,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>76899118</t>
+          <t>20968266</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12592,30 +12592,30 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>RAMOS</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>SERGIO FREDDY</t>
+          <t>ANGELICA PETRONILA</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F194" t="n">
-        <v>15</v>
+        <v>77</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>11/05/2011</t>
+          <t>31/05/1949</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>16/02/2022</t>
+          <t>20/06/2022</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -12645,45 +12645,45 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>20968266</t>
+          <t>75492572</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>RAMOS</t>
+          <t>RAYMUNDO</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>QUIÑONEZ</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>ANGELICA PETRONILA</t>
+          <t>SAUL MARLON</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F195" t="n">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>31/05/1949</t>
+          <t>06/01/2001</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
@@ -12693,7 +12693,7 @@
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>20/06/2022</t>
+          <t>08/11/2012</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
@@ -12708,7 +12708,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>75492572</t>
+          <t>74255598</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12723,20 +12723,20 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>SAUL MARLON</t>
+          <t>CYNTHIA LUCERO</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F196" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>06/01/2001</t>
+          <t>26/02/2006</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -12756,7 +12756,7 @@
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>08/11/2012</t>
+          <t>06/11/2012</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -12771,7 +12771,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>74255598</t>
+          <t>80846572</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12786,30 +12786,30 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>CYNTHIA LUCERO</t>
+          <t>PAUL BRAYAN</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F197" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>26/02/2006</t>
+          <t>24/06/2013</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
@@ -12819,7 +12819,7 @@
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>06/11/2012</t>
+          <t>15/05/2018</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -12834,22 +12834,22 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>80846572</t>
+          <t>19973981</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>RAYMUNDO</t>
+          <t>REBOLO</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>QUIÑONEZ</t>
+          <t>CAJA</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>PAUL BRAYAN</t>
+          <t>ALFONSO</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -12858,21 +12858,21 @@
         </is>
       </c>
       <c r="F198" t="n">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>24/06/2013</t>
+          <t>01/08/1973</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
@@ -12882,7 +12882,7 @@
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>15/05/2018</t>
+          <t>20/08/2014</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -12897,7 +12897,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>19973981</t>
+          <t>92844456</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -12907,12 +12907,12 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>CAJA</t>
+          <t>MORATILLO</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>ALFONSO</t>
+          <t>AXEL CALEB</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -12921,21 +12921,21 @@
         </is>
       </c>
       <c r="F199" t="n">
-        <v>53</v>
+        <v>4</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>01/08/1973</t>
+          <t>13/04/2022</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
@@ -12945,7 +12945,7 @@
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>20/08/2014</t>
+          <t>19/04/2022</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
@@ -12960,7 +12960,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>92844456</t>
+          <t>93507639</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -12975,20 +12975,20 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>AXEL CALEB</t>
+          <t>SOFIA YULIET</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F200" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>13/04/2022</t>
+          <t>18/08/2023</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -13008,7 +13008,7 @@
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>19/04/2022</t>
+          <t>22/08/2023</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
@@ -13023,7 +13023,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>93507639</t>
+          <t>76377604</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -13033,35 +13033,35 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>MORATILLO</t>
+          <t>SARZO</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>SOFIA YULIET</t>
+          <t>ELVIS FELEMON</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F201" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>18/08/2023</t>
+          <t>11/03/1995</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
@@ -13071,7 +13071,7 @@
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>22/08/2023</t>
+          <t>28/11/2014</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
@@ -13086,7 +13086,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>76377604</t>
+          <t>77203713</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -13101,20 +13101,20 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>ELVIS FELEMON</t>
+          <t>MARISOL SOLEDAD</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F202" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>11/03/1995</t>
+          <t>07/05/1996</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -13124,7 +13124,7 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
@@ -13134,7 +13134,7 @@
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>28/11/2014</t>
+          <t>15/05/2018</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
@@ -13149,7 +13149,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>77203713</t>
+          <t>76512760</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -13164,30 +13164,30 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>MARISOL SOLEDAD</t>
+          <t>AMADEO</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F203" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>07/05/1996</t>
+          <t>08/03/2002</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
@@ -13197,7 +13197,7 @@
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>15/05/2018</t>
+          <t>14/11/2013</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
@@ -13212,7 +13212,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>76512760</t>
+          <t>60010701</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -13227,20 +13227,20 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>AMADEO</t>
+          <t>DINA ROCIO</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F204" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>08/03/2002</t>
+          <t>15/05/2006</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -13250,7 +13250,7 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
@@ -13260,7 +13260,7 @@
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t>14/11/2013</t>
+          <t>10/03/2014</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
@@ -13275,7 +13275,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>60010701</t>
+          <t>61567977</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -13290,7 +13290,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>DINA ROCIO</t>
+          <t>RUTH KARINA</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -13299,11 +13299,11 @@
         </is>
       </c>
       <c r="F205" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>15/05/2006</t>
+          <t>05/10/2008</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -13323,7 +13323,7 @@
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>10/03/2014</t>
+          <t>14/11/2013</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
@@ -13338,7 +13338,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>61567977</t>
+          <t>81411624</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -13353,7 +13353,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>RUTH KARINA</t>
+          <t>JHOISE MILEY</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -13362,21 +13362,21 @@
         </is>
       </c>
       <c r="F206" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>05/10/2008</t>
+          <t>25/01/2014</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
@@ -13386,7 +13386,7 @@
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>14/11/2013</t>
+          <t>07/08/2014</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
@@ -13401,22 +13401,22 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>81411624</t>
+          <t>92213897</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>REBOLO</t>
+          <t>RENGIFO</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>SARZO</t>
+          <t>LLANCARI</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>JHOISE MILEY</t>
+          <t>GEYLY ALESSIA</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -13425,21 +13425,21 @@
         </is>
       </c>
       <c r="F207" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>25/01/2014</t>
+          <t>30/01/2021</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
@@ -13449,7 +13449,7 @@
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>07/08/2014</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
@@ -13464,22 +13464,22 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>92213897</t>
+          <t>20962028</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>RENGIFO</t>
+          <t>REVILLA</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>LLANCARI</t>
+          <t>BARAZORA</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>GEYLY ALESSIA</t>
+          <t>ESTELA</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -13488,21 +13488,21 @@
         </is>
       </c>
       <c r="F208" t="n">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>30/01/2021</t>
+          <t>18/02/1961</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>12/12/2012</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
@@ -13527,22 +13527,22 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>20962028</t>
+          <t>44654907</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>REVILLA</t>
+          <t>RIVERA</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>BARAZORA</t>
+          <t>REZA</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>ESTELA</t>
+          <t>DELIA</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -13551,16 +13551,16 @@
         </is>
       </c>
       <c r="F209" t="n">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>18/02/1961</t>
+          <t>06/10/1981</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -13575,7 +13575,7 @@
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>12/12/2012</t>
+          <t>21/03/2024</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
@@ -13590,35 +13590,35 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>21009438</t>
+          <t>48351631</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>RIOS</t>
+          <t>RIVERA</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>ZUMAETA</t>
+          <t>VALERO</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>CELIA</t>
+          <t>TINO JULIO</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F210" t="n">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>10/02/1969</t>
+          <t>13/08/1983</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -13638,7 +13638,7 @@
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>28/06/2011</t>
+          <t>22/06/2018</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
@@ -13653,7 +13653,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>44654907</t>
+          <t>20998172</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -13663,30 +13663,30 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>REZA</t>
+          <t>VELIZ</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>DELIA</t>
+          <t>PEDRO</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F211" t="n">
-        <v>45</v>
+        <v>79</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>06/10/1981</t>
+          <t>28/08/1947</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -13701,7 +13701,7 @@
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t>21/03/2024</t>
+          <t>14/05/2015</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
@@ -13716,40 +13716,40 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>48351631</t>
+          <t>23641374</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t>ROCA</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>VALERO</t>
+          <t>DE LA CRUZ</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>TINO JULIO</t>
+          <t>VICTORIA</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F212" t="n">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>13/08/1983</t>
+          <t>11/12/1964</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -13764,7 +13764,7 @@
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>22/06/2018</t>
+          <t>14/05/2015</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
@@ -13779,40 +13779,40 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>20998172</t>
+          <t>81411658</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>VELIZ</t>
+          <t>CASTILLO</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>PEDRO</t>
+          <t>LUANA LUZ</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F213" t="n">
-        <v>79</v>
+        <v>12</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>28/08/1947</t>
+          <t>30/05/2014</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -13827,7 +13827,7 @@
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t>14/05/2015</t>
+          <t>21/06/2016</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
@@ -13842,22 +13842,22 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>23641374</t>
+          <t>92339956</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>ROCA</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>DE LA CRUZ</t>
+          <t>LLANCO</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>VICTORIA</t>
+          <t>NIHAN SURI</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -13866,16 +13866,16 @@
         </is>
       </c>
       <c r="F214" t="n">
-        <v>62</v>
+        <v>5</v>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>11/12/1964</t>
+          <t>01/05/2021</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -13890,7 +13890,7 @@
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t>14/05/2015</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
@@ -13905,7 +13905,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>81411658</t>
+          <t>60248608</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -13915,12 +13915,12 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>CASTILLO</t>
+          <t>MARMANILLA</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>LUANA LUZ</t>
+          <t>SHELA MAYLI</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -13929,21 +13929,21 @@
         </is>
       </c>
       <c r="F215" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>30/05/2014</t>
+          <t>16/03/2007</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
@@ -13953,7 +13953,7 @@
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>21/06/2016</t>
+          <t>26/05/2015</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
@@ -13968,7 +13968,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>92339956</t>
+          <t>44023916</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -13978,30 +13978,30 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>LLANCO</t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>NIHAN SURI</t>
+          <t>MAGNO DUARTE</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F216" t="n">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>01/05/2021</t>
+          <t>01/01/1987</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -14016,7 +14016,7 @@
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>18/08/2015</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
@@ -14031,7 +14031,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>60248608</t>
+          <t>72912528</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -14041,12 +14041,12 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>MARMANILLA</t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>SHELA MAYLI</t>
+          <t>BRIGGITT MEYBE</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -14055,21 +14055,21 @@
         </is>
       </c>
       <c r="F217" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>16/03/2007</t>
+          <t>05/02/1995</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
@@ -14079,7 +14079,7 @@
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>26/05/2015</t>
+          <t>24/04/2024</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
@@ -14094,7 +14094,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>44023916</t>
+          <t>20968235</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -14104,12 +14104,12 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t>QUINTO</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>MAGNO DUARTE</t>
+          <t>FERNANDO</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -14118,16 +14118,16 @@
         </is>
       </c>
       <c r="F218" t="n">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>01/01/1987</t>
+          <t>09/02/1959</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -14142,7 +14142,7 @@
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>18/08/2015</t>
+          <t>17/11/2014</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
@@ -14157,22 +14157,22 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>72912528</t>
+          <t>20995529</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>SALAZAR</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t>MUÑOZ</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>BRIGGITT MEYBE</t>
+          <t>SARA LUZ</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -14181,11 +14181,11 @@
         </is>
       </c>
       <c r="F219" t="n">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>05/02/1995</t>
+          <t>05/12/1973</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -14195,7 +14195,7 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
@@ -14205,7 +14205,7 @@
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t>24/04/2024</t>
+          <t>20/02/2012</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
@@ -14220,45 +14220,45 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>20968235</t>
+          <t>20038651</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>QUINTO</t>
+          <t>TELLO</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>FERNANDO</t>
+          <t>SELENE YANNET</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F220" t="n">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>09/02/1959</t>
+          <t>06/04/1972</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
@@ -14268,7 +14268,7 @@
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t>17/11/2014</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
@@ -14283,22 +14283,22 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>20995529</t>
+          <t>19973976</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>SALAZAR</t>
+          <t>SARZO</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>MUÑOZ</t>
+          <t>MAURICIO</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>SARA LUZ</t>
+          <t>AURELIA</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -14307,11 +14307,11 @@
         </is>
       </c>
       <c r="F221" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>05/12/1973</t>
+          <t>13/11/1975</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -14331,7 +14331,7 @@
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t>20/02/2012</t>
+          <t>20/08/2014</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
@@ -14346,35 +14346,35 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>20038651</t>
+          <t>47918352</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>SAUÑI</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>TELLO</t>
+          <t>COSME</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>SELENE YANNET</t>
+          <t>LUIS FELIPE</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F222" t="n">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>06/04/1972</t>
+          <t>25/11/1989</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -14384,7 +14384,7 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
@@ -14394,7 +14394,7 @@
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>25/05/2016</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
@@ -14409,40 +14409,40 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>19973976</t>
+          <t>90815601</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>SARZO</t>
+          <t>SAUÑI</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>MAURICIO</t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>AURELIA</t>
+          <t>YAHIR IKER</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F223" t="n">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>13/11/1975</t>
+          <t>10/06/2018</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -14457,7 +14457,7 @@
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t>20/08/2014</t>
+          <t>10/06/2023</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
@@ -14472,22 +14472,22 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>47918352</t>
+          <t>20086058</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>SAUÑI</t>
+          <t>SEBASTIAN</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>COSME</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>LUIS FELIPE</t>
+          <t>JUAN</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -14496,16 +14496,16 @@
         </is>
       </c>
       <c r="F224" t="n">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>25/11/1989</t>
+          <t>19/10/1957</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -14520,7 +14520,7 @@
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t>25/05/2016</t>
+          <t>28/06/2011</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
@@ -14535,40 +14535,40 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>90815601</t>
+          <t>72619127</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>SAUÑI</t>
+          <t>SEBASTIAN</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t>RIOS</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>YAHIR IKER</t>
+          <t>GISENIA</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F225" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>10/06/2018</t>
+          <t>10/01/2003</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -14583,7 +14583,7 @@
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t>10/06/2023</t>
+          <t>14/12/2012</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
@@ -14598,22 +14598,22 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>20086058</t>
+          <t>43776143</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>SEBASTIAN</t>
+          <t>SEDANO</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>CCOICCA</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>JUAN</t>
+          <t>JULIO CESAR</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -14622,21 +14622,21 @@
         </is>
       </c>
       <c r="F226" t="n">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>19/10/1957</t>
+          <t>26/07/1986</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
@@ -14646,7 +14646,7 @@
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t>28/06/2011</t>
+          <t>25/09/2023</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
@@ -14661,22 +14661,22 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>72619127</t>
+          <t>93171977</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>SEBASTIAN</t>
+          <t>SEDANO</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>RIOS</t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>GISENIA</t>
+          <t>ALESSIA MILAGROS</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -14685,21 +14685,21 @@
         </is>
       </c>
       <c r="F227" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>10/01/2003</t>
+          <t>09/12/2022</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
@@ -14709,7 +14709,7 @@
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t>14/12/2012</t>
+          <t>14/12/2022</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
@@ -14724,45 +14724,45 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>43776143</t>
+          <t>63152228</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>SEDANO</t>
+          <t>SHAMAYRE</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>CCOICCA</t>
+          <t>BONIFACIO</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>JULIO CESAR</t>
+          <t>SHEYLA JELEN</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F228" t="n">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>26/07/1986</t>
+          <t>28/12/2012</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
@@ -14772,7 +14772,7 @@
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t>25/09/2023</t>
+          <t>09/06/2014</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
@@ -14787,22 +14787,22 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>93171977</t>
+          <t>81479827</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>SEDANO</t>
+          <t>SHAMAYRE</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t>BONIFACIO</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>ALESSIA MILAGROS</t>
+          <t>NASHELY JEYDI</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -14811,11 +14811,11 @@
         </is>
       </c>
       <c r="F229" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>09/12/2022</t>
+          <t>11/04/2015</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -14825,7 +14825,7 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
@@ -14835,7 +14835,7 @@
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t>14/12/2022</t>
+          <t>29/05/2020</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
@@ -14850,7 +14850,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>63152228</t>
+          <t>62076738</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -14860,30 +14860,30 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>BONIFACIO</t>
+          <t>MURAYARI</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>SHEYLA JELEN</t>
+          <t>YELSIN</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F230" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>28/12/2012</t>
+          <t>31/07/1996</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -14913,45 +14913,45 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>81479827</t>
+          <t>20997942</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>SHAMAYRE</t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>BONIFACIO</t>
+          <t>ADRIANO</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>NASHELY JEYDI</t>
+          <t>CLAUDIO</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F231" t="n">
-        <v>11</v>
+        <v>60</v>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>11/04/2015</t>
+          <t>03/12/1966</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
@@ -14961,7 +14961,7 @@
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t>29/05/2020</t>
+          <t>16/12/2015</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
@@ -14976,45 +14976,45 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>62076738</t>
+          <t>62188640</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>SHAMAYRE</t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>MURAYARI</t>
+          <t>ALCALA</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>YELSIN</t>
+          <t>MADHAI YULIANA</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F232" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>31/07/1996</t>
+          <t>25/11/2010</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
@@ -15024,7 +15024,7 @@
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t>09/06/2014</t>
+          <t>20/06/2022</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
@@ -15039,7 +15039,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>20997942</t>
+          <t>44299876</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -15049,12 +15049,12 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>ADRIANO</t>
+          <t>ARAUJO</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>CLAUDIO</t>
+          <t>NICOLAS</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -15063,16 +15063,16 @@
         </is>
       </c>
       <c r="F233" t="n">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>03/12/1966</t>
+          <t>05/06/1987</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -15087,7 +15087,7 @@
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t>16/12/2015</t>
+          <t>02/12/2015</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
@@ -15102,7 +15102,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>62188640</t>
+          <t>45944785</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -15112,12 +15112,12 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>ALCALA</t>
+          <t>ARAUJO</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>MADHAI YULIANA</t>
+          <t>SONIA</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -15126,21 +15126,21 @@
         </is>
       </c>
       <c r="F234" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>25/11/2010</t>
+          <t>30/08/1989</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
@@ -15150,7 +15150,7 @@
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t>20/06/2022</t>
+          <t>27/01/2015</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
@@ -15165,7 +15165,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>44299876</t>
+          <t>73658335</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -15180,7 +15180,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>NICOLAS</t>
+          <t>ALFREDO</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -15189,11 +15189,11 @@
         </is>
       </c>
       <c r="F235" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>05/06/1987</t>
+          <t>07/12/1996</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -15213,7 +15213,7 @@
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t>02/12/2015</t>
+          <t>20/08/2014</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
@@ -15228,7 +15228,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>45944785</t>
+          <t>20990269</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -15238,35 +15238,35 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>ARAUJO</t>
+          <t>PORRAS</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>SONIA</t>
+          <t>JAIME</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F236" t="n">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>30/08/1989</t>
+          <t>11/01/1961</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
@@ -15276,7 +15276,7 @@
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t>27/01/2015</t>
+          <t>23/10/2013</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
@@ -15291,7 +15291,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>73658335</t>
+          <t>43183658</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -15301,25 +15301,25 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>ARAUJO</t>
+          <t>VELASCO</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>ALFREDO</t>
+          <t>MERY MILAGROS</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F237" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>07/12/1996</t>
+          <t>13/07/1985</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -15329,7 +15329,7 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
@@ -15339,7 +15339,7 @@
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t>20/08/2014</t>
+          <t>24/05/2018</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
@@ -15354,7 +15354,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>20990269</t>
+          <t>44423352</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -15364,30 +15364,30 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>PORRAS</t>
+          <t>VELASCO</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>JAIME</t>
+          <t>YESELA YESSICA</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F238" t="n">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>11/01/1961</t>
+          <t>16/04/1987</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -15417,7 +15417,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>43183658</t>
+          <t>73668036</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -15432,7 +15432,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>MERY MILAGROS</t>
+          <t>THALIA VICTORIA</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -15441,21 +15441,21 @@
         </is>
       </c>
       <c r="F239" t="n">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>13/07/1985</t>
+          <t>11/10/1997</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
@@ -15465,7 +15465,7 @@
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t>24/05/2018</t>
+          <t>23/01/2014</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
@@ -15480,35 +15480,35 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>44423352</t>
+          <t>47735179</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t>TELLO</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>VELASCO</t>
+          <t>DE LA O</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>YESELA YESSICA</t>
+          <t>CLINTON VLADIMIR</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F240" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>16/04/1987</t>
+          <t>12/04/1993</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -15518,7 +15518,7 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t>23/10/2013</t>
+          <t>21/05/2021</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
@@ -15543,22 +15543,22 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>73668036</t>
+          <t>46443405</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t>TELLO</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>VELASCO</t>
+          <t>DELAO</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>THALIA VICTORIA</t>
+          <t>SUSAN CLEIVEN</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -15567,21 +15567,21 @@
         </is>
       </c>
       <c r="F241" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>11/10/1997</t>
+          <t>24/07/1990</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
@@ -15591,7 +15591,7 @@
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t>23/01/2014</t>
+          <t>29/05/2020</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
@@ -15606,7 +15606,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>47735179</t>
+          <t>62188641</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -15616,12 +15616,12 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>DE LA O</t>
+          <t>HINOSTROZA</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>CLINTON VLADIMIR</t>
+          <t>JHAN JULIAN</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -15630,21 +15630,21 @@
         </is>
       </c>
       <c r="F242" t="n">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>12/04/1993</t>
+          <t>15/11/2010</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
@@ -15654,7 +15654,7 @@
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t>21/05/2021</t>
+          <t>24/06/2013</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
@@ -15669,7 +15669,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>46443405</t>
+          <t>80846587</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -15679,12 +15679,12 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>DELAO</t>
+          <t>HINOSTROZA</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>SUSAN CLEIVEN</t>
+          <t>LIZMAR VALENTINA</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -15693,21 +15693,21 @@
         </is>
       </c>
       <c r="F243" t="n">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>24/07/1990</t>
+          <t>27/07/2013</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
@@ -15717,7 +15717,7 @@
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t>29/05/2020</t>
+          <t>22/06/2018</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
@@ -15732,7 +15732,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>62188641</t>
+          <t>92883208</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -15747,30 +15747,30 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>JHAN JULIAN</t>
+          <t>BRITNEY ZAYNEP</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F244" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>15/11/2010</t>
+          <t>09/05/2022</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
@@ -15780,7 +15780,7 @@
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t>24/06/2013</t>
+          <t>13/05/2022</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
@@ -15795,7 +15795,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>80846587</t>
+          <t>76779569</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -15805,35 +15805,35 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>HINOSTROZA</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>LIZMAR VALENTINA</t>
+          <t>ROY MAX</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F245" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>27/07/2013</t>
+          <t>05/01/2002</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
@@ -15843,7 +15843,7 @@
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t>22/06/2018</t>
+          <t>23/05/2018</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
@@ -15858,7 +15858,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>92883208</t>
+          <t>60804074</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -15868,12 +15868,12 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>HINOSTROZA</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>BRITNEY ZAYNEP</t>
+          <t>MEDALIT INES</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -15882,21 +15882,21 @@
         </is>
       </c>
       <c r="F246" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>09/05/2022</t>
+          <t>13/09/2006</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
@@ -15906,7 +15906,7 @@
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t>13/05/2022</t>
+          <t>14/11/2013</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
@@ -15921,7 +15921,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>76779569</t>
+          <t>90483077</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -15936,30 +15936,30 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>ROY MAX</t>
+          <t>KAROL YURA</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F247" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>05/01/2002</t>
+          <t>14/10/2017</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
@@ -15969,7 +15969,7 @@
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t>23/05/2018</t>
+          <t>14/10/2022</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
@@ -15984,7 +15984,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>60804074</t>
+          <t>20961171</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -15994,35 +15994,35 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>RIVERA</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>MEDALIT INES</t>
+          <t>CESAR JORGE</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F248" t="n">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>13/09/2006</t>
+          <t>23/04/1954</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
@@ -16032,7 +16032,7 @@
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t>14/11/2013</t>
+          <t>06/05/2014</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
@@ -16047,7 +16047,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>90483077</t>
+          <t>20997672</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -16057,35 +16057,35 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>RIVERA</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>KAROL YURA</t>
+          <t>MIGUEL</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F249" t="n">
-        <v>9</v>
+        <v>58</v>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>14/10/2017</t>
+          <t>29/09/1968</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
@@ -16095,7 +16095,7 @@
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t>14/10/2022</t>
+          <t>24/10/2018</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
@@ -16110,7 +16110,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>20961171</t>
+          <t>62666623</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -16120,12 +16120,12 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>CESAR JORGE</t>
+          <t>YUSTIN STALIN</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -16134,16 +16134,16 @@
         </is>
       </c>
       <c r="F250" t="n">
-        <v>72</v>
+        <v>16</v>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>23/04/1954</t>
+          <t>19/10/2010</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -16158,7 +16158,7 @@
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t>06/05/2014</t>
+          <t>10/03/2014</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
@@ -16173,22 +16173,22 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>20997672</t>
+          <t>91176371</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>TELLO</t>
+          <t>TENORIO</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>MIGUEL</t>
+          <t>THIAGO ESNAYDER</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -16197,21 +16197,21 @@
         </is>
       </c>
       <c r="F251" t="n">
-        <v>58</v>
+        <v>7</v>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>29/09/1968</t>
+          <t>09/02/2019</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
@@ -16221,7 +16221,7 @@
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t>24/10/2018</t>
+          <t>09/02/2024</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
@@ -16236,40 +16236,40 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>62666623</t>
+          <t>48606480</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>TELLO</t>
+          <t>TINEO</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>CARBAJAL</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>YUSTIN STALIN</t>
+          <t>CARMEN</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F252" t="n">
-        <v>16</v>
+        <v>78</v>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>19/10/2010</t>
+          <t>08/08/1948</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
@@ -16284,7 +16284,7 @@
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t>10/03/2014</t>
+          <t>06/06/2013</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
@@ -16299,22 +16299,22 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>91176371</t>
+          <t>76961463</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>TENORIO</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>ALVAREZ</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>THIAGO ESNAYDER</t>
+          <t>EDVIS ANLLE</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -16323,21 +16323,21 @@
         </is>
       </c>
       <c r="F253" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>09/02/2019</t>
+          <t>09/06/2000</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
@@ -16347,7 +16347,7 @@
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t>09/02/2024</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
@@ -16362,22 +16362,22 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>48606480</t>
+          <t>73392208</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>TINEO</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>CARBAJAL</t>
+          <t>BRAVO</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>CARMEN</t>
+          <t>MARIAEMILIA AQUILINA</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -16386,16 +16386,16 @@
         </is>
       </c>
       <c r="F254" t="n">
-        <v>78</v>
+        <v>20</v>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>08/08/1948</t>
+          <t>02/02/2006</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -16410,7 +16410,7 @@
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t>06/06/2013</t>
+          <t>14/11/2013</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
@@ -16425,40 +16425,40 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>79670987</t>
+          <t>46640139</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>TORPOCO</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t>BULLON</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>BON JOVI LEO DAN</t>
+          <t>ASHLYN EVELIN</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F255" t="n">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>08/05/2016</t>
+          <t>08/09/1989</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -16473,7 +16473,7 @@
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t>01/09/2025</t>
+          <t>02/05/2025</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
@@ -16488,7 +16488,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>73392208</t>
+          <t>20997838</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -16498,35 +16498,35 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>BRAVO</t>
+          <t>GIL</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>MARIAEMILIA AQUILINA</t>
+          <t>ALFONSO MARIO</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F256" t="n">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>02/02/2006</t>
+          <t>24/01/1972</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
@@ -16536,7 +16536,7 @@
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t>14/11/2013</t>
+          <t>23/10/2013</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
@@ -16551,7 +16551,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>46640139</t>
+          <t>41327149</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -16561,12 +16561,12 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>BULLON</t>
+          <t>GIL</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>ASHLYN EVELIN</t>
+          <t>YOLANDA</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -16575,11 +16575,11 @@
         </is>
       </c>
       <c r="F257" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>08/09/1989</t>
+          <t>29/12/1981</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -16589,7 +16589,7 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
@@ -16599,7 +16599,7 @@
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t>02/05/2025</t>
+          <t>23/10/2013</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
@@ -16614,45 +16614,45 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>20997838</t>
+          <t>16298521</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>TUPIÑO</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>GIL</t>
+          <t>CHUPAYO</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>ALFONSO MARIO</t>
+          <t>MAGNA EUFRACIA</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F258" t="n">
-        <v>54</v>
+        <v>91</v>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>24/01/1972</t>
+          <t>23/03/1935</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
@@ -16662,7 +16662,7 @@
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t>23/10/2013</t>
+          <t>21/02/2018</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
@@ -16677,45 +16677,45 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>41327149</t>
+          <t>93036344</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>TUPIÑO</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>GIL</t>
+          <t>ELIAS</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>YOLANDA</t>
+          <t>YELSIN ENDRICK</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F259" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>29/12/1981</t>
+          <t>27/08/2022</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
@@ -16725,7 +16725,7 @@
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t>23/10/2013</t>
+          <t>08/09/2022</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
@@ -16740,22 +16740,22 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>16298521</t>
+          <t>93520229</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>TUPIÑO</t>
+          <t>UNTIVEROS</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>CHUPAYO</t>
+          <t>CAJA</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>MAGNA EUFRACIA</t>
+          <t>CAROLINA MILAGROS</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -16764,21 +16764,21 @@
         </is>
       </c>
       <c r="F260" t="n">
-        <v>91</v>
+        <v>3</v>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>23/03/1935</t>
+          <t>29/08/2023</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
@@ -16788,7 +16788,7 @@
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t>21/02/2018</t>
+          <t>01/09/2023</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
@@ -16803,22 +16803,22 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>93036344</t>
+          <t>19954220</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>TUPIÑO</t>
+          <t>URETA</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>ELIAS</t>
+          <t>LORENZO</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>YELSIN ENDRICK</t>
+          <t>ENRIQUE ANTONIO</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -16827,21 +16827,21 @@
         </is>
       </c>
       <c r="F261" t="n">
-        <v>4</v>
+        <v>62</v>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>27/08/2022</t>
+          <t>21/01/1964</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
@@ -16851,7 +16851,7 @@
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t>08/09/2022</t>
+          <t>17/05/2012</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
@@ -16866,45 +16866,45 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>93520229</t>
+          <t>20984663</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>UNTIVEROS</t>
+          <t>VALERIO</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>CAJA</t>
+          <t>ITURRIZAGA</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>CAROLINA MILAGROS</t>
+          <t>WILLIAM HOMAR</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F262" t="n">
-        <v>3</v>
+        <v>69</v>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>29/08/2023</t>
+          <t>02/10/1957</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
@@ -16914,7 +16914,7 @@
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t>01/09/2023</t>
+          <t>23/10/2013</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
@@ -16929,22 +16929,22 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>19954220</t>
+          <t>23154367</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>URETA</t>
+          <t>VARGAS</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>LORENZO</t>
+          <t>NAJARRO</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>ENRIQUE ANTONIO</t>
+          <t>GREGORIO</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -16953,11 +16953,11 @@
         </is>
       </c>
       <c r="F263" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>21/01/1964</t>
+          <t>02/06/1957</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -16977,7 +16977,7 @@
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t>17/05/2012</t>
+          <t>11/09/2020</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
@@ -16992,22 +16992,22 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>20984663</t>
+          <t>74252864</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>VALERIO</t>
+          <t>VELASCO</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>ITURRIZAGA</t>
+          <t>BALTAZAR</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>WILLIAM HOMAR</t>
+          <t>EDUARDO HIGOR</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -17016,21 +17016,21 @@
         </is>
       </c>
       <c r="F264" t="n">
-        <v>69</v>
+        <v>25</v>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>02/10/1957</t>
+          <t>13/05/2001</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
@@ -17040,7 +17040,7 @@
       </c>
       <c r="K264" t="inlineStr">
         <is>
-          <t>23/10/2013</t>
+          <t>22/10/2012</t>
         </is>
       </c>
       <c r="L264" t="inlineStr">
@@ -17055,22 +17055,22 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>23154367</t>
+          <t>20968964</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>VARGAS</t>
+          <t>VELASCO</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>NAJARRO</t>
+          <t>LEON</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>GREGORIO</t>
+          <t>AMADEO</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -17079,16 +17079,16 @@
         </is>
       </c>
       <c r="F265" t="n">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>02/06/1957</t>
+          <t>12/09/1967</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
@@ -17103,7 +17103,7 @@
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t>11/09/2020</t>
+          <t>30/09/2017</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
@@ -17118,7 +17118,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>74252864</t>
+          <t>20997654</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -17128,12 +17128,12 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>BALTAZAR</t>
+          <t>LEON</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>EDUARDO HIGOR</t>
+          <t>EVER</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -17142,16 +17142,16 @@
         </is>
       </c>
       <c r="F266" t="n">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>13/05/2001</t>
+          <t>18/07/1969</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
@@ -17166,7 +17166,7 @@
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t>22/10/2012</t>
+          <t>29/12/2015</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
@@ -17181,7 +17181,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>20968964</t>
+          <t>20968854</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -17191,35 +17191,35 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>LEON</t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>AMADEO</t>
+          <t>ELENA</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F267" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>12/09/1967</t>
+          <t>31/08/1965</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
@@ -17229,7 +17229,7 @@
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t>30/09/2017</t>
+          <t>23/10/2013</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
@@ -17244,7 +17244,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>20997654</t>
+          <t>73668031</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -17254,12 +17254,12 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>LEON</t>
+          <t>SALAZAR</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>EVER</t>
+          <t>WALDIR EVER</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -17268,16 +17268,16 @@
         </is>
       </c>
       <c r="F268" t="n">
-        <v>57</v>
+        <v>26</v>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>18/07/1969</t>
+          <t>17/02/2000</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -17307,45 +17307,45 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>20968854</t>
+          <t>73660273</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>VELASCO</t>
+          <t>VELI</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t>CASTILLO</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>ELENA</t>
+          <t>ABNER ISAI</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F269" t="n">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>31/08/1965</t>
+          <t>18/11/1999</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
@@ -17355,7 +17355,7 @@
       </c>
       <c r="K269" t="inlineStr">
         <is>
-          <t>23/10/2013</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
@@ -17370,22 +17370,22 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>73668031</t>
+          <t>77168884</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>VELASCO</t>
+          <t>VELIZ</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>SALAZAR</t>
+          <t>AVILA</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>WALDIR EVER</t>
+          <t>ALEX VICTOR</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -17394,11 +17394,11 @@
         </is>
       </c>
       <c r="F270" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>17/02/2000</t>
+          <t>02/03/2002</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -17418,7 +17418,7 @@
       </c>
       <c r="K270" t="inlineStr">
         <is>
-          <t>29/12/2015</t>
+          <t>02/05/2013</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
@@ -17433,45 +17433,45 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>73660273</t>
+          <t>20968333</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>VELI</t>
+          <t>VELIZ</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>CASTILLO</t>
+          <t>BALTAZAR</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>ABNER ISAI</t>
+          <t>MARIA</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F271" t="n">
-        <v>27</v>
+        <v>69</v>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>18/11/1999</t>
+          <t>14/09/1957</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
@@ -17481,7 +17481,7 @@
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>20/08/2014</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
@@ -17496,7 +17496,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>77168884</t>
+          <t>48597551</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -17506,12 +17506,12 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>AVILA</t>
+          <t>CALDERON</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>ALEX VICTOR</t>
+          <t>JHON TOÑO</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
@@ -17520,16 +17520,16 @@
         </is>
       </c>
       <c r="F272" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>02/03/2002</t>
+          <t>16/03/1994</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -17544,7 +17544,7 @@
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t>02/05/2013</t>
+          <t>17/09/2020</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
@@ -17559,7 +17559,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>20968333</t>
+          <t>74459055</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -17569,30 +17569,30 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>BALTAZAR</t>
+          <t>CALDERON</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>MARIA</t>
+          <t>RUBEN</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F273" t="n">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>14/09/1957</t>
+          <t>01/07/1999</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -17607,7 +17607,7 @@
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t>20/08/2014</t>
+          <t>09/03/2015</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
@@ -17622,7 +17622,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>48597551</t>
+          <t>75605556</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -17637,7 +17637,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>JHON TOÑO</t>
+          <t>CRISTHIAN</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -17646,21 +17646,21 @@
         </is>
       </c>
       <c r="F274" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>16/03/1994</t>
+          <t>25/10/2002</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
@@ -17670,7 +17670,7 @@
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t>17/09/2020</t>
+          <t>14/11/2013</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
@@ -17685,7 +17685,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>74459055</t>
+          <t>60366737</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -17700,7 +17700,7 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>RUBEN</t>
+          <t>WILLIAN</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -17709,21 +17709,21 @@
         </is>
       </c>
       <c r="F275" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>01/07/1999</t>
+          <t>29/06/2009</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
@@ -17733,7 +17733,7 @@
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t>09/03/2015</t>
+          <t>23/01/2014</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
@@ -17748,7 +17748,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>75605556</t>
+          <t>63039413</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -17763,30 +17763,30 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>CRISTHIAN</t>
+          <t>SHAILA MAYOMI</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F276" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>25/10/2002</t>
+          <t>19/06/2012</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>RESIDENTES CC.PP. FOCALIZADOS (DL N° 1164)</t>
         </is>
       </c>
       <c r="J276" t="inlineStr">
@@ -17796,7 +17796,7 @@
       </c>
       <c r="K276" t="inlineStr">
         <is>
-          <t>14/11/2013</t>
+          <t>10/11/2015</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
@@ -17811,7 +17811,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>60366737</t>
+          <t>61697283</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -17821,17 +17821,17 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>CALDERON</t>
+          <t>HINOSTROZA</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>WILLIAN</t>
+          <t>KANDY ALINA</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F277" t="n">
@@ -17839,7 +17839,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>29/06/2009</t>
+          <t>12/09/2009</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -17849,7 +17849,7 @@
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J277" t="inlineStr">
@@ -17859,7 +17859,7 @@
       </c>
       <c r="K277" t="inlineStr">
         <is>
-          <t>23/01/2014</t>
+          <t>15/05/2025</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
@@ -17874,7 +17874,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>63039413</t>
+          <t>20093098</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -17884,12 +17884,12 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>CALDERON</t>
+          <t>HUALLPA</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>SHAILA MAYOMI</t>
+          <t>OLGA VICTORIA</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -17898,21 +17898,21 @@
         </is>
       </c>
       <c r="F278" t="n">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>19/06/2012</t>
+          <t>21/11/1971</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>RESIDENTES CC.PP. FOCALIZADOS (DL N° 1164)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J278" t="inlineStr">
@@ -17922,7 +17922,7 @@
       </c>
       <c r="K278" t="inlineStr">
         <is>
-          <t>10/11/2015</t>
+          <t>22/06/2012</t>
         </is>
       </c>
       <c r="L278" t="inlineStr">
@@ -17937,7 +17937,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>61697283</t>
+          <t>80633727</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -17947,12 +17947,12 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>HINOSTROZA</t>
+          <t>NUÑEZ</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>KANDY ALINA</t>
+          <t>ELVA</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -17961,21 +17961,21 @@
         </is>
       </c>
       <c r="F279" t="n">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>12/09/2009</t>
+          <t>22/02/1979</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J279" t="inlineStr">
@@ -17985,7 +17985,7 @@
       </c>
       <c r="K279" t="inlineStr">
         <is>
-          <t>15/05/2025</t>
+          <t>29/10/2014</t>
         </is>
       </c>
       <c r="L279" t="inlineStr">
@@ -18000,7 +18000,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>20093098</t>
+          <t>20092028</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -18010,25 +18010,25 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>HUALLPA</t>
+          <t>RICCE</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>OLGA VICTORIA</t>
+          <t>BERNARDINO</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F280" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>21/11/1971</t>
+          <t>25/09/1972</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -18048,7 +18048,7 @@
       </c>
       <c r="K280" t="inlineStr">
         <is>
-          <t>22/06/2012</t>
+          <t>07/08/2014</t>
         </is>
       </c>
       <c r="L280" t="inlineStr">
@@ -18063,22 +18063,22 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>80633727</t>
+          <t>61697334</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>VELIZ</t>
+          <t>VERA</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>NUÑEZ</t>
+          <t>MALDONADO</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>ELVA</t>
+          <t>RUTH FIORELLA</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -18087,21 +18087,21 @@
         </is>
       </c>
       <c r="F281" t="n">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>22/02/1979</t>
+          <t>23/04/2010</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
@@ -18111,7 +18111,7 @@
       </c>
       <c r="K281" t="inlineStr">
         <is>
-          <t>29/10/2014</t>
+          <t>10/03/2014</t>
         </is>
       </c>
       <c r="L281" t="inlineStr">
@@ -18126,45 +18126,45 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>20092028</t>
+          <t>63410556</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>VELIZ</t>
+          <t>VERA</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>RICCE</t>
+          <t>MALDONADO</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>BERNARDINO</t>
+          <t>MARICIELO</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F282" t="n">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>25/09/1972</t>
+          <t>19/07/2011</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
@@ -18174,7 +18174,7 @@
       </c>
       <c r="K282" t="inlineStr">
         <is>
-          <t>07/08/2014</t>
+          <t>07/03/2012</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
@@ -18189,7 +18189,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>61697334</t>
+          <t>76698356</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -18199,35 +18199,35 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>MALDONADO</t>
+          <t>UNCHUPAICO</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>RUTH FIORELLA</t>
+          <t>EDIL</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F283" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>23/04/2010</t>
+          <t>26/09/1999</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
@@ -18237,7 +18237,7 @@
       </c>
       <c r="K283" t="inlineStr">
         <is>
-          <t>10/03/2014</t>
+          <t>07/12/2020</t>
         </is>
       </c>
       <c r="L283" t="inlineStr">
@@ -18252,7 +18252,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>63410556</t>
+          <t>77217052</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -18262,12 +18262,12 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>MALDONADO</t>
+          <t>UNCHUPAICO</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>MARICIELO</t>
+          <t>JIMENA</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -18276,21 +18276,21 @@
         </is>
       </c>
       <c r="F284" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>19/07/2011</t>
+          <t>10/03/2003</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
@@ -18300,7 +18300,7 @@
       </c>
       <c r="K284" t="inlineStr">
         <is>
-          <t>07/03/2012</t>
+          <t>23/10/2012</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
@@ -18315,22 +18315,22 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>76698356</t>
+          <t>73668010</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>VERA</t>
+          <t>VICENTE</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>UNCHUPAICO</t>
+          <t>GONZALES</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>EDIL</t>
+          <t>NELSIN GUERNIZ</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -18339,11 +18339,11 @@
         </is>
       </c>
       <c r="F285" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>26/09/1999</t>
+          <t>17/06/1998</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -18363,7 +18363,7 @@
       </c>
       <c r="K285" t="inlineStr">
         <is>
-          <t>07/12/2020</t>
+          <t>21/07/2017</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
@@ -18378,35 +18378,35 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>77217052</t>
+          <t>73660322</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>VERA</t>
+          <t>VICENTE</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>UNCHUPAICO</t>
+          <t>GONZALES</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>JIMENA</t>
+          <t>YINIBEL MIGNER</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F286" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>10/03/2003</t>
+          <t>05/10/2000</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -18416,7 +18416,7 @@
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
@@ -18426,7 +18426,7 @@
       </c>
       <c r="K286" t="inlineStr">
         <is>
-          <t>23/10/2012</t>
+          <t>24/05/2018</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
@@ -18441,7 +18441,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>73668010</t>
+          <t>73668009</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -18456,7 +18456,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>NELSIN GUERNIZ</t>
+          <t>LIZBEL</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -18465,11 +18465,11 @@
         </is>
       </c>
       <c r="F287" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>17/06/1998</t>
+          <t>07/10/2002</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -18489,7 +18489,7 @@
       </c>
       <c r="K287" t="inlineStr">
         <is>
-          <t>21/07/2017</t>
+          <t>14/11/2013</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
@@ -18504,7 +18504,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>73660322</t>
+          <t>74255587</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -18519,20 +18519,20 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>YINIBEL MIGNER</t>
+          <t>YANIRA MARLI</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F288" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>05/10/2000</t>
+          <t>16/06/2003</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -18552,7 +18552,7 @@
       </c>
       <c r="K288" t="inlineStr">
         <is>
-          <t>24/05/2018</t>
+          <t>16/02/2022</t>
         </is>
       </c>
       <c r="L288" t="inlineStr">
@@ -18567,7 +18567,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>73668009</t>
+          <t>61567970</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -18582,20 +18582,20 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>LIZBEL</t>
+          <t>MABEL GUDELIA</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F289" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>07/10/2002</t>
+          <t>14/09/2008</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -18605,7 +18605,7 @@
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
@@ -18615,7 +18615,7 @@
       </c>
       <c r="K289" t="inlineStr">
         <is>
-          <t>14/11/2013</t>
+          <t>09/03/2015</t>
         </is>
       </c>
       <c r="L289" t="inlineStr">
@@ -18630,7 +18630,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>74255587</t>
+          <t>63410580</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -18645,7 +18645,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>YANIRA MARLI</t>
+          <t>DILMA ESTRIT</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -18654,21 +18654,21 @@
         </is>
       </c>
       <c r="F290" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>16/06/2003</t>
+          <t>25/10/2011</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
@@ -18678,7 +18678,7 @@
       </c>
       <c r="K290" t="inlineStr">
         <is>
-          <t>16/02/2022</t>
+          <t>09/03/2015</t>
         </is>
       </c>
       <c r="L290" t="inlineStr">
@@ -18693,7 +18693,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>61567970</t>
+          <t>80846527</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -18708,7 +18708,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>MABEL GUDELIA</t>
+          <t>NATALI YERIT</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -18717,21 +18717,21 @@
         </is>
       </c>
       <c r="F291" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>14/09/2008</t>
+          <t>19/10/2012</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
@@ -18741,7 +18741,7 @@
       </c>
       <c r="K291" t="inlineStr">
         <is>
-          <t>09/03/2015</t>
+          <t>16/09/2013</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
@@ -18756,7 +18756,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>63410580</t>
+          <t>80846586</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -18771,20 +18771,20 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>DILMA ESTRIT</t>
+          <t>BRINNER ADLER</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F292" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>25/10/2011</t>
+          <t>29/07/2013</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -18794,7 +18794,7 @@
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J292" t="inlineStr">
@@ -18804,7 +18804,7 @@
       </c>
       <c r="K292" t="inlineStr">
         <is>
-          <t>09/03/2015</t>
+          <t>24/09/2018</t>
         </is>
       </c>
       <c r="L292" t="inlineStr">
@@ -18819,7 +18819,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>80846527</t>
+          <t>16298489</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -18829,30 +18829,30 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>GONZALES</t>
+          <t>HUAMAN</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>NATALI YERIT</t>
+          <t>ANASTACIO GERMIAS</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F293" t="n">
-        <v>14</v>
+        <v>72</v>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>19/10/2012</t>
+          <t>05/05/1954</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -18867,7 +18867,7 @@
       </c>
       <c r="K293" t="inlineStr">
         <is>
-          <t>16/09/2013</t>
+          <t>14/07/2017</t>
         </is>
       </c>
       <c r="L293" t="inlineStr">
@@ -18882,7 +18882,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>80846586</t>
+          <t>16298675</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -18892,12 +18892,12 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>GONZALES</t>
+          <t>HUAMAN</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>BRINNER ADLER</t>
+          <t>FELIPE EULOGIO</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -18906,16 +18906,16 @@
         </is>
       </c>
       <c r="F294" t="n">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>29/07/2013</t>
+          <t>20/09/1969</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -18930,7 +18930,7 @@
       </c>
       <c r="K294" t="inlineStr">
         <is>
-          <t>24/09/2018</t>
+          <t>30/09/2017</t>
         </is>
       </c>
       <c r="L294" t="inlineStr">
@@ -18945,7 +18945,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>16298489</t>
+          <t>16298763</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -18960,7 +18960,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>ANASTACIO GERMIAS</t>
+          <t>JUSTINO VICTOR</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -18969,16 +18969,16 @@
         </is>
       </c>
       <c r="F295" t="n">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>05/05/1954</t>
+          <t>14/05/1973</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -18993,7 +18993,7 @@
       </c>
       <c r="K295" t="inlineStr">
         <is>
-          <t>14/07/2017</t>
+          <t>30/08/2011</t>
         </is>
       </c>
       <c r="L295" t="inlineStr">
@@ -19008,7 +19008,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>16298675</t>
+          <t>41320935</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -19023,7 +19023,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>FELIPE EULOGIO</t>
+          <t>MISAEL ELIAS</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -19032,11 +19032,11 @@
         </is>
       </c>
       <c r="F296" t="n">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>20/09/1969</t>
+          <t>16/11/1981</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -19056,7 +19056,7 @@
       </c>
       <c r="K296" t="inlineStr">
         <is>
-          <t>30/09/2017</t>
+          <t>14/07/2017</t>
         </is>
       </c>
       <c r="L296" t="inlineStr">
@@ -19071,7 +19071,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>16298763</t>
+          <t>78377550</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -19086,25 +19086,25 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>JUSTINO VICTOR</t>
+          <t>YHIMLI EDDITH</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F297" t="n">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>14/05/1973</t>
+          <t>19/06/2005</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -19119,7 +19119,7 @@
       </c>
       <c r="K297" t="inlineStr">
         <is>
-          <t>30/08/2011</t>
+          <t>01/03/2016</t>
         </is>
       </c>
       <c r="L297" t="inlineStr">
@@ -19134,7 +19134,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>41320935</t>
+          <t>60369319</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -19149,30 +19149,30 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>MISAEL ELIAS</t>
+          <t>LUZ MARIELA</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F298" t="n">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>16/11/1981</t>
+          <t>18/03/2008</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
@@ -19182,7 +19182,7 @@
       </c>
       <c r="K298" t="inlineStr">
         <is>
-          <t>14/07/2017</t>
+          <t>10/03/2014</t>
         </is>
       </c>
       <c r="L298" t="inlineStr">
@@ -19197,7 +19197,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>78377550</t>
+          <t>62188608</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -19212,30 +19212,30 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>YHIMLI EDDITH</t>
+          <t>BELARMINO GOYTIER</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F299" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>19/06/2005</t>
+          <t>14/08/2010</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
@@ -19260,7 +19260,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>60369319</t>
+          <t>47241610</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -19270,35 +19270,35 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>HUAMAN</t>
+          <t>TUPIÑO</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>LUZ MARIELA</t>
+          <t>DOMNER ELMER</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F300" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>18/03/2008</t>
+          <t>19/08/1992</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
@@ -19308,7 +19308,7 @@
       </c>
       <c r="K300" t="inlineStr">
         <is>
-          <t>10/03/2014</t>
+          <t>11/08/2015</t>
         </is>
       </c>
       <c r="L300" t="inlineStr">
@@ -19323,7 +19323,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>62188608</t>
+          <t>76480084</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -19333,12 +19333,12 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>HUAMAN</t>
+          <t>TUPIÑO</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>BELARMINO GOYTIER</t>
+          <t>MEGDONIO MILDER</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -19347,21 +19347,21 @@
         </is>
       </c>
       <c r="F301" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>14/08/2010</t>
+          <t>29/08/1994</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J301" t="inlineStr">
@@ -19371,7 +19371,7 @@
       </c>
       <c r="K301" t="inlineStr">
         <is>
-          <t>01/03/2016</t>
+          <t>16/04/2013</t>
         </is>
       </c>
       <c r="L301" t="inlineStr">
@@ -19386,7 +19386,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>47241610</t>
+          <t>81526383</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -19396,12 +19396,12 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>TUPIÑO</t>
+          <t>ZARZO</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>DOMNER ELMER</t>
+          <t>YADIEL DAHYVINSU</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -19410,16 +19410,16 @@
         </is>
       </c>
       <c r="F302" t="n">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>19/08/1992</t>
+          <t>06/07/2017</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -19434,7 +19434,7 @@
       </c>
       <c r="K302" t="inlineStr">
         <is>
-          <t>11/08/2015</t>
+          <t>06/07/2022</t>
         </is>
       </c>
       <c r="L302" t="inlineStr">
@@ -19449,7 +19449,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>76480084</t>
+          <t>90665716</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -19459,12 +19459,12 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>TUPIÑO</t>
+          <t>ZARZO</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>MEGDONIO MILDER</t>
+          <t>YENMIR ELMER</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -19473,16 +19473,16 @@
         </is>
       </c>
       <c r="F303" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>29/08/1994</t>
+          <t>07/03/2018</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -19497,7 +19497,7 @@
       </c>
       <c r="K303" t="inlineStr">
         <is>
-          <t>16/04/2013</t>
+          <t>07/03/2023</t>
         </is>
       </c>
       <c r="L303" t="inlineStr">
@@ -19512,40 +19512,40 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>81526383</t>
+          <t>20968047</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>VICENTE</t>
+          <t>YALLICO</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>ZARZO</t>
+          <t>DE SUELDO</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>YADIEL DAHYVINSU</t>
+          <t>CATALINA</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F304" t="n">
-        <v>9</v>
+        <v>84</v>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>06/07/2017</t>
+          <t>18/11/1942</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -19560,7 +19560,7 @@
       </c>
       <c r="K304" t="inlineStr">
         <is>
-          <t>06/07/2022</t>
+          <t>28/11/2014</t>
         </is>
       </c>
       <c r="L304" t="inlineStr">
@@ -19575,40 +19575,40 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>90665716</t>
+          <t>48787947</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>VICENTE</t>
+          <t>ZARZO</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>ZARZO</t>
+          <t>LEONARDO</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>YENMIR ELMER</t>
+          <t>NANCY YANET</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F305" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>07/03/2018</t>
+          <t>17/02/1995</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -19623,7 +19623,7 @@
       </c>
       <c r="K305" t="inlineStr">
         <is>
-          <t>07/03/2023</t>
+          <t>06/05/2014</t>
         </is>
       </c>
       <c r="L305" t="inlineStr">
@@ -19638,40 +19638,40 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>20968047</t>
+          <t>76764813</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>YALLICO</t>
+          <t>ZARZO</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>DE SUELDO</t>
+          <t>LEONARDO</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>CATALINA</t>
+          <t>NERIO YHONVERZON</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F306" t="n">
-        <v>84</v>
+        <v>29</v>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>18/11/1942</t>
+          <t>22/07/1997</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -19686,7 +19686,7 @@
       </c>
       <c r="K306" t="inlineStr">
         <is>
-          <t>28/11/2014</t>
+          <t>22/12/2011</t>
         </is>
       </c>
       <c r="L306" t="inlineStr">
@@ -19701,7 +19701,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>48787947</t>
+          <t>77498210</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -19716,7 +19716,7 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>NANCY YANET</t>
+          <t>JUDTH SOLEDAD</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
@@ -19725,16 +19725,16 @@
         </is>
       </c>
       <c r="F307" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>17/02/1995</t>
+          <t>03/02/2000</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -19749,7 +19749,7 @@
       </c>
       <c r="K307" t="inlineStr">
         <is>
-          <t>06/05/2014</t>
+          <t>23/10/2012</t>
         </is>
       </c>
       <c r="L307" t="inlineStr">
@@ -19764,7 +19764,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>76764813</t>
+          <t>19973654</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -19774,12 +19774,12 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>LEONARDO</t>
+          <t>MAURICIO</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>NERIO YHONVERZON</t>
+          <t>ESTEBAN JESUS</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
@@ -19788,16 +19788,16 @@
         </is>
       </c>
       <c r="F308" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>22/07/1997</t>
+          <t>26/12/1973</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -19821,132 +19821,6 @@
         </is>
       </c>
       <c r="M308" t="n">
-        <v>120602</v>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" t="inlineStr">
-        <is>
-          <t>77498210</t>
-        </is>
-      </c>
-      <c r="B309" t="inlineStr">
-        <is>
-          <t>ZARZO</t>
-        </is>
-      </c>
-      <c r="C309" t="inlineStr">
-        <is>
-          <t>LEONARDO</t>
-        </is>
-      </c>
-      <c r="D309" t="inlineStr">
-        <is>
-          <t>JUDTH SOLEDAD</t>
-        </is>
-      </c>
-      <c r="E309" t="inlineStr">
-        <is>
-          <t>Femenino</t>
-        </is>
-      </c>
-      <c r="F309" t="n">
-        <v>26</v>
-      </c>
-      <c r="G309" t="inlineStr">
-        <is>
-          <t>03/02/2000</t>
-        </is>
-      </c>
-      <c r="H309" t="inlineStr">
-        <is>
-          <t>3.JOVEN</t>
-        </is>
-      </c>
-      <c r="I309" t="inlineStr">
-        <is>
-          <t>AFILIACION PPDD</t>
-        </is>
-      </c>
-      <c r="J309" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K309" t="inlineStr">
-        <is>
-          <t>23/10/2012</t>
-        </is>
-      </c>
-      <c r="L309" t="inlineStr">
-        <is>
-          <t>COVIRIALI</t>
-        </is>
-      </c>
-      <c r="M309" t="n">
-        <v>120602</v>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310" t="inlineStr">
-        <is>
-          <t>19973654</t>
-        </is>
-      </c>
-      <c r="B310" t="inlineStr">
-        <is>
-          <t>ZARZO</t>
-        </is>
-      </c>
-      <c r="C310" t="inlineStr">
-        <is>
-          <t>MAURICIO</t>
-        </is>
-      </c>
-      <c r="D310" t="inlineStr">
-        <is>
-          <t>ESTEBAN JESUS</t>
-        </is>
-      </c>
-      <c r="E310" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
-      <c r="F310" t="n">
-        <v>53</v>
-      </c>
-      <c r="G310" t="inlineStr">
-        <is>
-          <t>26/12/1973</t>
-        </is>
-      </c>
-      <c r="H310" t="inlineStr">
-        <is>
-          <t>4.ADULTO</t>
-        </is>
-      </c>
-      <c r="I310" t="inlineStr">
-        <is>
-          <t>AFILIACION PPDD</t>
-        </is>
-      </c>
-      <c r="J310" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K310" t="inlineStr">
-        <is>
-          <t>22/12/2011</t>
-        </is>
-      </c>
-      <c r="L310" t="inlineStr">
-        <is>
-          <t>COVIRIALI</t>
-        </is>
-      </c>
-      <c r="M310" t="n">
         <v>120602</v>
       </c>
     </row>
